--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56594</v>
+        <v>56596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56598</v>
+        <v>56600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56596</v>
+        <v>56598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
+          <t>Andreas Estensen, Tonje Lindmark, Johan Engström, Markus Melber</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56600</v>
+        <v>56602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Tonje Lindmark, Johan Engström, Markus Melber</t>
+          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -804,7 +804,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
+          <t>Andreas Estensen, Tonje Lindmark, Johan Engström, Markus Melber</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56602</v>
+        <v>56605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56601</v>
+        <v>56753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56605</v>
+        <v>56757</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56753</v>
+        <v>56755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56757</v>
+        <v>56759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56755</v>
+        <v>56756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56759</v>
+        <v>56760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56761</v>
+        <v>56767</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56765</v>
+        <v>56771</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56767</v>
+        <v>56768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56771</v>
+        <v>56772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129218175</v>
       </c>
       <c r="B2" t="n">
-        <v>56768</v>
+        <v>56771</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56772</v>
+        <v>56775</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129218175</v>
+        <v>125573995</v>
       </c>
       <c r="B2" t="n">
-        <v>56771</v>
+        <v>56825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205988</v>
+        <v>102102</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tajgafladdermus</t>
+          <t>Mustaschfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis brandtii</t>
+          <t>Myotis mystacinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eversmann, 1845)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>fjolårsunge</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -723,11 +723,7 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -735,17 +731,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrfors Parkvägen bakom, Ång</t>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696617</v>
+        <v>696671</v>
       </c>
       <c r="R2" t="n">
-        <v>7077483</v>
+        <v>7077486</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -769,22 +765,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +795,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Markus Melber</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
+          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -818,7 +814,7 @@
         <v>129218330</v>
       </c>
       <c r="B3" t="n">
-        <v>56775</v>
+        <v>56825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -948,6 +944,428 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Fladdermusdata handbestämning</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125576241</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56821</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>205988</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tajgafladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Myotis brandtii</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Eversmann, 1845)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>slöjnät</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>696671</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7077486</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>22:08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Markus Melber</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fladdermusdata handbestämning</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129218153</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56821</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205988</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tajgafladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Myotis brandtii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Eversmann, 1845)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>slöjnät</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norrfors Parkvägen bakom, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>696617</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7077483</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-06</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>01:10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Markus Melber</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Markus Melber, Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Fladdermusdata handbestämning</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125573771</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>slöjnät</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>696671</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7077486</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Trädgård</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Andreas Estensen</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Andreas Estensen, Markus Melber, Johan Engström, Tonje Lindmark, Michael Schneider, Erik Owusu-Ansah</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Fladdermusdata handbestämning</t>
         </is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125573995</v>
+        <v>135290704</v>
       </c>
       <c r="B2" t="n">
-        <v>56825</v>
+        <v>98133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102102</v>
+        <v>167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mustaschfladdermus</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis mystacinus</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>slöjnät</t>
-        </is>
-      </c>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
@@ -765,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,18 +775,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Fladdermusdata handbestämning</t>
-        </is>
-      </c>
+          <t>Andreas Estensen, Johan Engström, Tonje Lindmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129218330</v>
+        <v>125573995</v>
       </c>
       <c r="B3" t="n">
         <v>56825</v>
@@ -851,19 +822,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -871,17 +838,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrfors Parkvägen bakom, Ång</t>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696617</v>
+        <v>696671</v>
       </c>
       <c r="R3" t="n">
-        <v>7077483</v>
+        <v>7077486</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -905,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,12 +902,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Melber</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
+          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -951,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125576241</v>
+        <v>129218330</v>
       </c>
       <c r="B4" t="n">
-        <v>56821</v>
+        <v>56825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -962,21 +929,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205988</v>
+        <v>102102</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgafladdermus</t>
+          <t>Mustaschfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis brandtii</t>
+          <t>Myotis mystacinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eversmann, 1845)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -996,10 +963,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -1007,17 +978,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+          <t>Norrfors Parkvägen bakom, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696671</v>
+        <v>696617</v>
       </c>
       <c r="R4" t="n">
-        <v>7077486</v>
+        <v>7077483</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1041,22 +1012,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1067,21 +1038,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Markus Melber</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Estensen</t>
+          <t>Markus Melber</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
+          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1092,7 +1058,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129218153</v>
+        <v>125576241</v>
       </c>
       <c r="B5" t="n">
         <v>56821</v>
@@ -1140,11 +1106,7 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -1152,17 +1114,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrfors Parkvägen bakom, Ång</t>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696617</v>
+        <v>696671</v>
       </c>
       <c r="R5" t="n">
-        <v>7077483</v>
+        <v>7077486</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1186,22 +1148,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1212,16 +1174,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Markus Melber</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Melber</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Melber, Johan Engström</t>
+          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1232,10 +1199,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125573771</v>
+        <v>129218153</v>
       </c>
       <c r="B6" t="n">
-        <v>56823</v>
+        <v>56821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,21 +1210,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>205988</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Tajgafladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Myotis brandtii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Eversmann, 1845)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1277,10 +1244,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -1288,17 +1259,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+          <t>Norrfors Parkvägen bakom, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696671</v>
+        <v>696617</v>
       </c>
       <c r="R6" t="n">
-        <v>7077486</v>
+        <v>7077483</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1322,22 +1293,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1348,24 +1319,160 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Trädgård</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Markus Melber</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Melber, Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Fladdermusdata handbestämning</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125573771</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>slöjnät</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>696671</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7077486</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Trädgård</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Andreas Estensen</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Andreas Estensen, Markus Melber, Johan Engström, Tonje Lindmark, Michael Schneider, Erik Owusu-Ansah</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Fladdermusdata handbestämning</t>
         </is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135290704</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
           <t>Fladdermusdata handbestämning</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125573995</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1055,6 +1070,11 @@
           <t>Fladdermusdata handbestämning</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129218330</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1196,6 +1216,11 @@
           <t>Fladdermusdata handbestämning</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125576241</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1336,6 +1361,11 @@
           <t>Fladdermusdata handbestämning</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129218153</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1477,8 +1507,21 @@
           <t>Fladdermusdata handbestämning</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125573771</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135290704</v>
       </c>
       <c r="B2" t="n">
-        <v>98133</v>
+        <v>98177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135290704</v>
       </c>
       <c r="B2" t="n">
-        <v>98177</v>
+        <v>98204</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,60 +680,35 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125573995</v>
+        <v>135290704</v>
       </c>
       <c r="B2" t="n">
-        <v>56825</v>
+        <v>98209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102102</v>
+        <v>167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mustaschfladdermus</t>
+          <t>Höstlåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis mystacinus</t>
+          <t>Botrychium multifidum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>slöjnät</t>
-        </is>
-      </c>
+          <t>(S. G. Gmel.) Rupr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
@@ -770,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>21:25</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,23 +780,19 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Fladdermusdata handbestämning</t>
-        </is>
-      </c>
+          <t>Andreas Estensen, Johan Engström, Tonje Lindmark</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125573995</t>
+          <t>https://artportalen.se/Sighting/135290704</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129218330</v>
+        <v>125573995</v>
       </c>
       <c r="B3" t="n">
         <v>56825</v>
@@ -861,19 +832,15 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>adult</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -881,17 +848,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrfors Parkvägen bakom, Ång</t>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696617</v>
+        <v>696671</v>
       </c>
       <c r="R3" t="n">
-        <v>7077483</v>
+        <v>7077486</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -915,22 +882,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>23:30</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -945,12 +912,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Melber</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
+          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -960,16 +927,16 @@
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129218330</t>
+          <t>https://artportalen.se/Sighting/125573995</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125576241</v>
+        <v>129218330</v>
       </c>
       <c r="B4" t="n">
-        <v>56821</v>
+        <v>56825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -977,21 +944,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>205988</v>
+        <v>102102</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tajgafladdermus</t>
+          <t>Mustaschfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Myotis brandtii</t>
+          <t>Myotis mystacinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eversmann, 1845)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1011,10 +978,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -1022,17 +993,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+          <t>Norrfors Parkvägen bakom, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>696671</v>
+        <v>696617</v>
       </c>
       <c r="R4" t="n">
-        <v>7077486</v>
+        <v>7077483</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1056,22 +1027,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>22:08</t>
+          <t>23:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1082,21 +1053,16 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Markus Melber</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Estensen</t>
+          <t>Markus Melber</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
+          <t>Markus Melber, Johan Engström, Tonje Lindmark, Andreas Estensen</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1106,13 +1072,13 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125576241</t>
+          <t>https://artportalen.se/Sighting/129218330</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129218153</v>
+        <v>125576241</v>
       </c>
       <c r="B5" t="n">
         <v>56821</v>
@@ -1160,11 +1126,7 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -1172,17 +1134,17 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrfors Parkvägen bakom, Ång</t>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>696617</v>
+        <v>696671</v>
       </c>
       <c r="R5" t="n">
-        <v>7077483</v>
+        <v>7077486</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1206,22 +1168,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-06</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>01:10</t>
+          <t>22:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1232,16 +1194,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Markus Melber</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Markus Melber</t>
+          <t>Andreas Estensen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Markus Melber, Johan Engström</t>
+          <t>Andreas Estensen, Markus Melber, Johan Engström, Michael Schneider, Erik Owusu-Ansah, Tonje Lindmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1251,16 +1218,16 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129218153</t>
+          <t>https://artportalen.se/Sighting/125576241</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125573771</v>
+        <v>129218153</v>
       </c>
       <c r="B6" t="n">
-        <v>56823</v>
+        <v>56821</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,21 +1235,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205992</v>
+        <v>205988</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Tajgafladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Myotis brandtii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Eversmann, 1845)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1302,10 +1269,14 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
           <t>slöjnät</t>
@@ -1313,17 +1284,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+          <t>Norrfors Parkvägen bakom, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>696671</v>
+        <v>696617</v>
       </c>
       <c r="R6" t="n">
-        <v>7077486</v>
+        <v>7077483</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1347,22 +1318,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2025-07-06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>01:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1373,29 +1344,170 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Trädgård</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Markus Melber</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Markus Melber, Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Fladdermusdata handbestämning</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129218153</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>125573771</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>slöjnät</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Parkvägen 1, Norrfors Nordmaling, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>696671</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7077486</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nordmaling</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Trädgård</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Andreas Estensen</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Andreas Estensen, Markus Melber, Johan Engström, Tonje Lindmark, Michael Schneider, Erik Owusu-Ansah</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr">
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Fladdermusdata handbestämning</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
+      <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125573771</t>
         </is>
@@ -1408,6 +1520,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 19667-2022 artfynd.xlsx
+++ b/artfynd/A 19667-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135290704</v>
       </c>
       <c r="B2" t="n">
-        <v>98209</v>
+        <v>98211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
